--- a/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsACH_23.xlsx
+++ b/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsACH_23.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="51">
   <si>
     <t>Result</t>
   </si>
@@ -147,6 +147,45 @@
   </si>
   <si>
     <t>Fri Jun 12 20:55:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 07:15:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 07:23:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 07:31:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 07:40:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 08:00:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 08:11:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 08:22:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 08:33:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 08:56:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 09:04:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 09:13:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 09:22:30 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -485,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -533,6 +572,12 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>50</v>
+      </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
@@ -573,7 +618,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DB9ADE0-3126-459F-BDC7-5A3E4FDB9131}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" bestFit="true" customWidth="true" width="8.44140625" collapsed="true"/>
@@ -624,11 +669,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>33</v>
+      <c r="A2" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>46</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -670,7 +715,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E913AF3D-2401-4143-A03C-AD443E0E7FBD}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -718,11 +763,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
+      <c r="A2" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>42</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -764,7 +809,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63200ADD-D811-48DC-9EEF-A67AE5458802}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -812,10 +857,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>29</v>
       </c>
       <c r="C2" s="2"/>
@@ -858,7 +903,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54F075A6-D0C1-4D29-90AD-B52B91921144}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -906,10 +951,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C2" s="2"/>
@@ -952,7 +997,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{007B8DDC-C724-4658-A3D7-E23303EBF7BC}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1000,10 +1045,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>35</v>
       </c>
       <c r="C2" s="2"/>
@@ -1046,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{760E4E4D-F035-4C23-A12D-E46C571C1A68}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1094,10 +1139,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>32</v>
       </c>
       <c r="C2" s="2"/>
@@ -1140,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89A7A183-B95B-43C9-8918-285E3A235DE1}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1188,10 +1233,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>37</v>
       </c>
       <c r="C2" s="2"/>
@@ -1234,7 +1279,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA266EF4-930C-4CA4-A5C3-C425F7B0AB76}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
